--- a/templates/Bank_Ledger_Template.xlsx
+++ b/templates/Bank_Ledger_Template.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7310"/>
   </bookViews>
   <sheets>
-    <sheet name="SIB Ledger MIS" sheetId="1" r:id="rId1"/>
+    <sheet name="Ledger Template" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -15203,217 +15203,779 @@
     <row r="992" ht="16.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="1016">
-    <mergeCell ref="L373:M373"/>
-    <mergeCell ref="L374:M374"/>
-    <mergeCell ref="L375:M375"/>
-    <mergeCell ref="R369:S369"/>
-    <mergeCell ref="R370:S370"/>
-    <mergeCell ref="L371:M371"/>
-    <mergeCell ref="R371:S371"/>
-    <mergeCell ref="L372:M372"/>
-    <mergeCell ref="R372:S372"/>
-    <mergeCell ref="R373:S373"/>
-    <mergeCell ref="L378:M378"/>
-    <mergeCell ref="L379:M379"/>
-    <mergeCell ref="L380:M380"/>
-    <mergeCell ref="R374:S374"/>
-    <mergeCell ref="R375:S375"/>
-    <mergeCell ref="L376:M376"/>
-    <mergeCell ref="R376:S376"/>
-    <mergeCell ref="L377:M377"/>
-    <mergeCell ref="R377:S377"/>
-    <mergeCell ref="R378:S378"/>
-    <mergeCell ref="L383:M383"/>
-    <mergeCell ref="L384:M384"/>
-    <mergeCell ref="L385:M385"/>
-    <mergeCell ref="R379:S379"/>
-    <mergeCell ref="R380:S380"/>
-    <mergeCell ref="L381:M381"/>
-    <mergeCell ref="R381:S381"/>
-    <mergeCell ref="L382:M382"/>
-    <mergeCell ref="R382:S382"/>
-    <mergeCell ref="R383:S383"/>
-    <mergeCell ref="L388:M388"/>
-    <mergeCell ref="L389:M389"/>
-    <mergeCell ref="L390:M390"/>
-    <mergeCell ref="R384:S384"/>
-    <mergeCell ref="R385:S385"/>
-    <mergeCell ref="L386:M386"/>
-    <mergeCell ref="R386:S386"/>
-    <mergeCell ref="L387:M387"/>
-    <mergeCell ref="R387:S387"/>
-    <mergeCell ref="R388:S388"/>
-    <mergeCell ref="L393:M393"/>
-    <mergeCell ref="L394:M394"/>
-    <mergeCell ref="L395:M395"/>
-    <mergeCell ref="R389:S389"/>
-    <mergeCell ref="R390:S390"/>
-    <mergeCell ref="L391:M391"/>
-    <mergeCell ref="R391:S391"/>
-    <mergeCell ref="L392:M392"/>
-    <mergeCell ref="R392:S392"/>
-    <mergeCell ref="R393:S393"/>
-    <mergeCell ref="L398:M398"/>
-    <mergeCell ref="L399:M399"/>
-    <mergeCell ref="L400:M400"/>
-    <mergeCell ref="R394:S394"/>
-    <mergeCell ref="R395:S395"/>
-    <mergeCell ref="L396:M396"/>
-    <mergeCell ref="R396:S396"/>
-    <mergeCell ref="L397:M397"/>
-    <mergeCell ref="R397:S397"/>
-    <mergeCell ref="R398:S398"/>
-    <mergeCell ref="L403:M403"/>
-    <mergeCell ref="L404:M404"/>
-    <mergeCell ref="L405:M405"/>
-    <mergeCell ref="R399:S399"/>
-    <mergeCell ref="R400:S400"/>
-    <mergeCell ref="L401:M401"/>
-    <mergeCell ref="R401:S401"/>
-    <mergeCell ref="L402:M402"/>
-    <mergeCell ref="R402:S402"/>
-    <mergeCell ref="R403:S403"/>
-    <mergeCell ref="L408:M408"/>
-    <mergeCell ref="L409:M409"/>
-    <mergeCell ref="L410:M410"/>
-    <mergeCell ref="R404:S404"/>
-    <mergeCell ref="R405:S405"/>
-    <mergeCell ref="L406:M406"/>
-    <mergeCell ref="R406:S406"/>
-    <mergeCell ref="L407:M407"/>
-    <mergeCell ref="R407:S407"/>
-    <mergeCell ref="R408:S408"/>
-    <mergeCell ref="L413:M413"/>
-    <mergeCell ref="L414:M414"/>
-    <mergeCell ref="L415:M415"/>
-    <mergeCell ref="R409:S409"/>
-    <mergeCell ref="R410:S410"/>
-    <mergeCell ref="L411:M411"/>
-    <mergeCell ref="R411:S411"/>
-    <mergeCell ref="L412:M412"/>
-    <mergeCell ref="R412:S412"/>
-    <mergeCell ref="R413:S413"/>
-    <mergeCell ref="L418:M418"/>
-    <mergeCell ref="L419:M419"/>
-    <mergeCell ref="L420:M420"/>
-    <mergeCell ref="R414:S414"/>
-    <mergeCell ref="R415:S415"/>
-    <mergeCell ref="L416:M416"/>
-    <mergeCell ref="R416:S416"/>
-    <mergeCell ref="L417:M417"/>
-    <mergeCell ref="R417:S417"/>
-    <mergeCell ref="R418:S418"/>
-    <mergeCell ref="L423:M423"/>
-    <mergeCell ref="L424:M424"/>
-    <mergeCell ref="L425:M425"/>
-    <mergeCell ref="R419:S419"/>
-    <mergeCell ref="R420:S420"/>
-    <mergeCell ref="L421:M421"/>
-    <mergeCell ref="R421:S421"/>
-    <mergeCell ref="L422:M422"/>
-    <mergeCell ref="R422:S422"/>
-    <mergeCell ref="R423:S423"/>
-    <mergeCell ref="L428:M428"/>
-    <mergeCell ref="L429:M429"/>
-    <mergeCell ref="L430:M430"/>
-    <mergeCell ref="R424:S424"/>
-    <mergeCell ref="R425:S425"/>
-    <mergeCell ref="L426:M426"/>
-    <mergeCell ref="R426:S426"/>
-    <mergeCell ref="L427:M427"/>
-    <mergeCell ref="R427:S427"/>
-    <mergeCell ref="R428:S428"/>
-    <mergeCell ref="L433:M433"/>
-    <mergeCell ref="L434:M434"/>
-    <mergeCell ref="L435:M435"/>
-    <mergeCell ref="R429:S429"/>
-    <mergeCell ref="R430:S430"/>
-    <mergeCell ref="L431:M431"/>
-    <mergeCell ref="R431:S431"/>
-    <mergeCell ref="L432:M432"/>
-    <mergeCell ref="R432:S432"/>
-    <mergeCell ref="R433:S433"/>
-    <mergeCell ref="L438:M438"/>
-    <mergeCell ref="L439:M439"/>
-    <mergeCell ref="L440:M440"/>
-    <mergeCell ref="R434:S434"/>
-    <mergeCell ref="R435:S435"/>
-    <mergeCell ref="L436:M436"/>
-    <mergeCell ref="R436:S436"/>
-    <mergeCell ref="L437:M437"/>
-    <mergeCell ref="R437:S437"/>
-    <mergeCell ref="R438:S438"/>
-    <mergeCell ref="L478:M478"/>
-    <mergeCell ref="L479:M479"/>
-    <mergeCell ref="L480:M480"/>
-    <mergeCell ref="R474:S474"/>
-    <mergeCell ref="R475:S475"/>
-    <mergeCell ref="L476:M476"/>
-    <mergeCell ref="R476:S476"/>
-    <mergeCell ref="L477:M477"/>
-    <mergeCell ref="R477:S477"/>
-    <mergeCell ref="R478:S478"/>
-    <mergeCell ref="L483:M483"/>
-    <mergeCell ref="L484:M484"/>
-    <mergeCell ref="L485:M485"/>
-    <mergeCell ref="R479:S479"/>
-    <mergeCell ref="R480:S480"/>
-    <mergeCell ref="L481:M481"/>
-    <mergeCell ref="R481:S481"/>
-    <mergeCell ref="L482:M482"/>
-    <mergeCell ref="R482:S482"/>
-    <mergeCell ref="R483:S483"/>
-    <mergeCell ref="L505:M505"/>
-    <mergeCell ref="R499:S499"/>
-    <mergeCell ref="R500:S500"/>
-    <mergeCell ref="L501:M501"/>
-    <mergeCell ref="R501:S501"/>
-    <mergeCell ref="L502:M502"/>
-    <mergeCell ref="R502:S502"/>
-    <mergeCell ref="R503:S503"/>
-    <mergeCell ref="L488:M488"/>
-    <mergeCell ref="L489:M489"/>
-    <mergeCell ref="L490:M490"/>
-    <mergeCell ref="R484:S484"/>
-    <mergeCell ref="R485:S485"/>
-    <mergeCell ref="L486:M486"/>
-    <mergeCell ref="R486:S486"/>
-    <mergeCell ref="L487:M487"/>
-    <mergeCell ref="R487:S487"/>
-    <mergeCell ref="R488:S488"/>
-    <mergeCell ref="L493:M493"/>
-    <mergeCell ref="L494:M494"/>
-    <mergeCell ref="L495:M495"/>
-    <mergeCell ref="R489:S489"/>
-    <mergeCell ref="R490:S490"/>
-    <mergeCell ref="L491:M491"/>
-    <mergeCell ref="R491:S491"/>
-    <mergeCell ref="L492:M492"/>
-    <mergeCell ref="R492:S492"/>
-    <mergeCell ref="R493:S493"/>
-    <mergeCell ref="L164:M164"/>
-    <mergeCell ref="L165:M165"/>
-    <mergeCell ref="L166:M166"/>
-    <mergeCell ref="L167:M167"/>
-    <mergeCell ref="L168:M168"/>
-    <mergeCell ref="L169:M169"/>
-    <mergeCell ref="L170:M170"/>
-    <mergeCell ref="L171:M171"/>
-    <mergeCell ref="L172:M172"/>
-    <mergeCell ref="L173:M173"/>
-    <mergeCell ref="L174:M174"/>
-    <mergeCell ref="L175:M175"/>
-    <mergeCell ref="L176:M176"/>
-    <mergeCell ref="L177:M177"/>
-    <mergeCell ref="R182:S182"/>
-    <mergeCell ref="R183:S183"/>
-    <mergeCell ref="L178:M178"/>
-    <mergeCell ref="L179:M179"/>
-    <mergeCell ref="L180:M180"/>
-    <mergeCell ref="L181:M181"/>
-    <mergeCell ref="R181:S181"/>
-    <mergeCell ref="L182:M182"/>
-    <mergeCell ref="L183:M183"/>
+    <mergeCell ref="L368:M368"/>
+    <mergeCell ref="L369:M369"/>
+    <mergeCell ref="L370:M370"/>
+    <mergeCell ref="R364:S364"/>
+    <mergeCell ref="R365:S365"/>
+    <mergeCell ref="L366:M366"/>
+    <mergeCell ref="R366:S366"/>
+    <mergeCell ref="L367:M367"/>
+    <mergeCell ref="R367:S367"/>
+    <mergeCell ref="R368:S368"/>
+    <mergeCell ref="L358:M358"/>
+    <mergeCell ref="L359:M359"/>
+    <mergeCell ref="L360:M360"/>
+    <mergeCell ref="R354:S354"/>
+    <mergeCell ref="R355:S355"/>
+    <mergeCell ref="L356:M356"/>
+    <mergeCell ref="R356:S356"/>
+    <mergeCell ref="L357:M357"/>
+    <mergeCell ref="R357:S357"/>
+    <mergeCell ref="R358:S358"/>
+    <mergeCell ref="L363:M363"/>
+    <mergeCell ref="L364:M364"/>
+    <mergeCell ref="L365:M365"/>
+    <mergeCell ref="R359:S359"/>
+    <mergeCell ref="R360:S360"/>
+    <mergeCell ref="L361:M361"/>
+    <mergeCell ref="R361:S361"/>
+    <mergeCell ref="L362:M362"/>
+    <mergeCell ref="R362:S362"/>
+    <mergeCell ref="R363:S363"/>
+    <mergeCell ref="L348:M348"/>
+    <mergeCell ref="L349:M349"/>
+    <mergeCell ref="L350:M350"/>
+    <mergeCell ref="R344:S344"/>
+    <mergeCell ref="R345:S345"/>
+    <mergeCell ref="L346:M346"/>
+    <mergeCell ref="R346:S346"/>
+    <mergeCell ref="L347:M347"/>
+    <mergeCell ref="R347:S347"/>
+    <mergeCell ref="R348:S348"/>
+    <mergeCell ref="L353:M353"/>
+    <mergeCell ref="L354:M354"/>
+    <mergeCell ref="L355:M355"/>
+    <mergeCell ref="R349:S349"/>
+    <mergeCell ref="R350:S350"/>
+    <mergeCell ref="L351:M351"/>
+    <mergeCell ref="R351:S351"/>
+    <mergeCell ref="L352:M352"/>
+    <mergeCell ref="R352:S352"/>
+    <mergeCell ref="R353:S353"/>
+    <mergeCell ref="L338:M338"/>
+    <mergeCell ref="L339:M339"/>
+    <mergeCell ref="L340:M340"/>
+    <mergeCell ref="R334:S334"/>
+    <mergeCell ref="R335:S335"/>
+    <mergeCell ref="L336:M336"/>
+    <mergeCell ref="R336:S336"/>
+    <mergeCell ref="L337:M337"/>
+    <mergeCell ref="R337:S337"/>
+    <mergeCell ref="R338:S338"/>
+    <mergeCell ref="L343:M343"/>
+    <mergeCell ref="L344:M344"/>
+    <mergeCell ref="L345:M345"/>
+    <mergeCell ref="R339:S339"/>
+    <mergeCell ref="R340:S340"/>
+    <mergeCell ref="L341:M341"/>
+    <mergeCell ref="R341:S341"/>
+    <mergeCell ref="L342:M342"/>
+    <mergeCell ref="R342:S342"/>
+    <mergeCell ref="R343:S343"/>
+    <mergeCell ref="L328:M328"/>
+    <mergeCell ref="L329:M329"/>
+    <mergeCell ref="L330:M330"/>
+    <mergeCell ref="R324:S324"/>
+    <mergeCell ref="R325:S325"/>
+    <mergeCell ref="L326:M326"/>
+    <mergeCell ref="R326:S326"/>
+    <mergeCell ref="L327:M327"/>
+    <mergeCell ref="R327:S327"/>
+    <mergeCell ref="R328:S328"/>
+    <mergeCell ref="L333:M333"/>
+    <mergeCell ref="L334:M334"/>
+    <mergeCell ref="L335:M335"/>
+    <mergeCell ref="R329:S329"/>
+    <mergeCell ref="R330:S330"/>
+    <mergeCell ref="L331:M331"/>
+    <mergeCell ref="R331:S331"/>
+    <mergeCell ref="L332:M332"/>
+    <mergeCell ref="R332:S332"/>
+    <mergeCell ref="R333:S333"/>
+    <mergeCell ref="L318:M318"/>
+    <mergeCell ref="L319:M319"/>
+    <mergeCell ref="L320:M320"/>
+    <mergeCell ref="R314:S314"/>
+    <mergeCell ref="R315:S315"/>
+    <mergeCell ref="L316:M316"/>
+    <mergeCell ref="R316:S316"/>
+    <mergeCell ref="L317:M317"/>
+    <mergeCell ref="R317:S317"/>
+    <mergeCell ref="R318:S318"/>
+    <mergeCell ref="L323:M323"/>
+    <mergeCell ref="L324:M324"/>
+    <mergeCell ref="L325:M325"/>
+    <mergeCell ref="R319:S319"/>
+    <mergeCell ref="R320:S320"/>
+    <mergeCell ref="L321:M321"/>
+    <mergeCell ref="R321:S321"/>
+    <mergeCell ref="L322:M322"/>
+    <mergeCell ref="R322:S322"/>
+    <mergeCell ref="R323:S323"/>
+    <mergeCell ref="L308:M308"/>
+    <mergeCell ref="L309:M309"/>
+    <mergeCell ref="L310:M310"/>
+    <mergeCell ref="R304:S304"/>
+    <mergeCell ref="R305:S305"/>
+    <mergeCell ref="L306:M306"/>
+    <mergeCell ref="R306:S306"/>
+    <mergeCell ref="L307:M307"/>
+    <mergeCell ref="R307:S307"/>
+    <mergeCell ref="R308:S308"/>
+    <mergeCell ref="L313:M313"/>
+    <mergeCell ref="L314:M314"/>
+    <mergeCell ref="L315:M315"/>
+    <mergeCell ref="R309:S309"/>
+    <mergeCell ref="R310:S310"/>
+    <mergeCell ref="L311:M311"/>
+    <mergeCell ref="R311:S311"/>
+    <mergeCell ref="L312:M312"/>
+    <mergeCell ref="R312:S312"/>
+    <mergeCell ref="R313:S313"/>
+    <mergeCell ref="L298:M298"/>
+    <mergeCell ref="L299:M299"/>
+    <mergeCell ref="L300:M300"/>
+    <mergeCell ref="R294:S294"/>
+    <mergeCell ref="R295:S295"/>
+    <mergeCell ref="L296:M296"/>
+    <mergeCell ref="R296:S296"/>
+    <mergeCell ref="L297:M297"/>
+    <mergeCell ref="R297:S297"/>
+    <mergeCell ref="R298:S298"/>
+    <mergeCell ref="L303:M303"/>
+    <mergeCell ref="L304:M304"/>
+    <mergeCell ref="L305:M305"/>
+    <mergeCell ref="R299:S299"/>
+    <mergeCell ref="R300:S300"/>
+    <mergeCell ref="L301:M301"/>
+    <mergeCell ref="R301:S301"/>
+    <mergeCell ref="L302:M302"/>
+    <mergeCell ref="R302:S302"/>
+    <mergeCell ref="R303:S303"/>
+    <mergeCell ref="L288:M288"/>
+    <mergeCell ref="L289:M289"/>
+    <mergeCell ref="L290:M290"/>
+    <mergeCell ref="R284:S284"/>
+    <mergeCell ref="R285:S285"/>
+    <mergeCell ref="L286:M286"/>
+    <mergeCell ref="R286:S286"/>
+    <mergeCell ref="L287:M287"/>
+    <mergeCell ref="R287:S287"/>
+    <mergeCell ref="R288:S288"/>
+    <mergeCell ref="L293:M293"/>
+    <mergeCell ref="L294:M294"/>
+    <mergeCell ref="L295:M295"/>
+    <mergeCell ref="R289:S289"/>
+    <mergeCell ref="R290:S290"/>
+    <mergeCell ref="L291:M291"/>
+    <mergeCell ref="R291:S291"/>
+    <mergeCell ref="L292:M292"/>
+    <mergeCell ref="R292:S292"/>
+    <mergeCell ref="R293:S293"/>
+    <mergeCell ref="L278:M278"/>
+    <mergeCell ref="L279:M279"/>
+    <mergeCell ref="L280:M280"/>
+    <mergeCell ref="R274:S274"/>
+    <mergeCell ref="R275:S275"/>
+    <mergeCell ref="L276:M276"/>
+    <mergeCell ref="R276:S276"/>
+    <mergeCell ref="L277:M277"/>
+    <mergeCell ref="R277:S277"/>
+    <mergeCell ref="R278:S278"/>
+    <mergeCell ref="L283:M283"/>
+    <mergeCell ref="L284:M284"/>
+    <mergeCell ref="L285:M285"/>
+    <mergeCell ref="R279:S279"/>
+    <mergeCell ref="R280:S280"/>
+    <mergeCell ref="L281:M281"/>
+    <mergeCell ref="R281:S281"/>
+    <mergeCell ref="L282:M282"/>
+    <mergeCell ref="R282:S282"/>
+    <mergeCell ref="R283:S283"/>
+    <mergeCell ref="L268:M268"/>
+    <mergeCell ref="L269:M269"/>
+    <mergeCell ref="L270:M270"/>
+    <mergeCell ref="R264:S264"/>
+    <mergeCell ref="R265:S265"/>
+    <mergeCell ref="L266:M266"/>
+    <mergeCell ref="R266:S266"/>
+    <mergeCell ref="L267:M267"/>
+    <mergeCell ref="R267:S267"/>
+    <mergeCell ref="R268:S268"/>
+    <mergeCell ref="L273:M273"/>
+    <mergeCell ref="L274:M274"/>
+    <mergeCell ref="L275:M275"/>
+    <mergeCell ref="R269:S269"/>
+    <mergeCell ref="R270:S270"/>
+    <mergeCell ref="L271:M271"/>
+    <mergeCell ref="R271:S271"/>
+    <mergeCell ref="L272:M272"/>
+    <mergeCell ref="R272:S272"/>
+    <mergeCell ref="R273:S273"/>
+    <mergeCell ref="L258:M258"/>
+    <mergeCell ref="L259:M259"/>
+    <mergeCell ref="L260:M260"/>
+    <mergeCell ref="R254:S254"/>
+    <mergeCell ref="R255:S255"/>
+    <mergeCell ref="L256:M256"/>
+    <mergeCell ref="R256:S256"/>
+    <mergeCell ref="L257:M257"/>
+    <mergeCell ref="R257:S257"/>
+    <mergeCell ref="R258:S258"/>
+    <mergeCell ref="L263:M263"/>
+    <mergeCell ref="L264:M264"/>
+    <mergeCell ref="L265:M265"/>
+    <mergeCell ref="R259:S259"/>
+    <mergeCell ref="R260:S260"/>
+    <mergeCell ref="L261:M261"/>
+    <mergeCell ref="R261:S261"/>
+    <mergeCell ref="L262:M262"/>
+    <mergeCell ref="R262:S262"/>
+    <mergeCell ref="R263:S263"/>
+    <mergeCell ref="L248:M248"/>
+    <mergeCell ref="L249:M249"/>
+    <mergeCell ref="L250:M250"/>
+    <mergeCell ref="R244:S244"/>
+    <mergeCell ref="R245:S245"/>
+    <mergeCell ref="L246:M246"/>
+    <mergeCell ref="R246:S246"/>
+    <mergeCell ref="L247:M247"/>
+    <mergeCell ref="R247:S247"/>
+    <mergeCell ref="R248:S248"/>
+    <mergeCell ref="L253:M253"/>
+    <mergeCell ref="L254:M254"/>
+    <mergeCell ref="L255:M255"/>
+    <mergeCell ref="R249:S249"/>
+    <mergeCell ref="R250:S250"/>
+    <mergeCell ref="L251:M251"/>
+    <mergeCell ref="R251:S251"/>
+    <mergeCell ref="L252:M252"/>
+    <mergeCell ref="R252:S252"/>
+    <mergeCell ref="R253:S253"/>
+    <mergeCell ref="L238:M238"/>
+    <mergeCell ref="L239:M239"/>
+    <mergeCell ref="L240:M240"/>
+    <mergeCell ref="R234:S234"/>
+    <mergeCell ref="R235:S235"/>
+    <mergeCell ref="L236:M236"/>
+    <mergeCell ref="R236:S236"/>
+    <mergeCell ref="L237:M237"/>
+    <mergeCell ref="R237:S237"/>
+    <mergeCell ref="R238:S238"/>
+    <mergeCell ref="L243:M243"/>
+    <mergeCell ref="L244:M244"/>
+    <mergeCell ref="L245:M245"/>
+    <mergeCell ref="R239:S239"/>
+    <mergeCell ref="R240:S240"/>
+    <mergeCell ref="L241:M241"/>
+    <mergeCell ref="R241:S241"/>
+    <mergeCell ref="L242:M242"/>
+    <mergeCell ref="R242:S242"/>
+    <mergeCell ref="R243:S243"/>
+    <mergeCell ref="L228:M228"/>
+    <mergeCell ref="L229:M229"/>
+    <mergeCell ref="L230:M230"/>
+    <mergeCell ref="R224:S224"/>
+    <mergeCell ref="R225:S225"/>
+    <mergeCell ref="L226:M226"/>
+    <mergeCell ref="R226:S226"/>
+    <mergeCell ref="L227:M227"/>
+    <mergeCell ref="R227:S227"/>
+    <mergeCell ref="R228:S228"/>
+    <mergeCell ref="L233:M233"/>
+    <mergeCell ref="L234:M234"/>
+    <mergeCell ref="L235:M235"/>
+    <mergeCell ref="R229:S229"/>
+    <mergeCell ref="R230:S230"/>
+    <mergeCell ref="L231:M231"/>
+    <mergeCell ref="R231:S231"/>
+    <mergeCell ref="L232:M232"/>
+    <mergeCell ref="R232:S232"/>
+    <mergeCell ref="R233:S233"/>
+    <mergeCell ref="L218:M218"/>
+    <mergeCell ref="L219:M219"/>
+    <mergeCell ref="L220:M220"/>
+    <mergeCell ref="R214:S214"/>
+    <mergeCell ref="R215:S215"/>
+    <mergeCell ref="L216:M216"/>
+    <mergeCell ref="R216:S216"/>
+    <mergeCell ref="L217:M217"/>
+    <mergeCell ref="R217:S217"/>
+    <mergeCell ref="R218:S218"/>
+    <mergeCell ref="L223:M223"/>
+    <mergeCell ref="L224:M224"/>
+    <mergeCell ref="L225:M225"/>
+    <mergeCell ref="R219:S219"/>
+    <mergeCell ref="R220:S220"/>
+    <mergeCell ref="L221:M221"/>
+    <mergeCell ref="R221:S221"/>
+    <mergeCell ref="L222:M222"/>
+    <mergeCell ref="R222:S222"/>
+    <mergeCell ref="R223:S223"/>
+    <mergeCell ref="R204:S204"/>
+    <mergeCell ref="R205:S205"/>
+    <mergeCell ref="L206:M206"/>
+    <mergeCell ref="R206:S206"/>
+    <mergeCell ref="L207:M207"/>
+    <mergeCell ref="R207:S207"/>
+    <mergeCell ref="R208:S208"/>
+    <mergeCell ref="L213:M213"/>
+    <mergeCell ref="L214:M214"/>
+    <mergeCell ref="L215:M215"/>
+    <mergeCell ref="R209:S209"/>
+    <mergeCell ref="R210:S210"/>
+    <mergeCell ref="L211:M211"/>
+    <mergeCell ref="R211:S211"/>
+    <mergeCell ref="L212:M212"/>
+    <mergeCell ref="R212:S212"/>
+    <mergeCell ref="R213:S213"/>
+    <mergeCell ref="L162:M162"/>
+    <mergeCell ref="L163:M163"/>
+    <mergeCell ref="R195:S195"/>
+    <mergeCell ref="R196:S196"/>
+    <mergeCell ref="R188:S188"/>
+    <mergeCell ref="R189:S189"/>
+    <mergeCell ref="R190:S190"/>
+    <mergeCell ref="R191:S191"/>
+    <mergeCell ref="R192:S192"/>
+    <mergeCell ref="R193:S193"/>
+    <mergeCell ref="R194:S194"/>
+    <mergeCell ref="R198:S198"/>
+    <mergeCell ref="R199:S199"/>
+    <mergeCell ref="L194:M194"/>
+    <mergeCell ref="L195:M195"/>
+    <mergeCell ref="L196:M196"/>
+    <mergeCell ref="L197:M197"/>
+    <mergeCell ref="R197:S197"/>
+    <mergeCell ref="L198:M198"/>
+    <mergeCell ref="L199:M199"/>
+    <mergeCell ref="L184:M184"/>
+    <mergeCell ref="R184:S184"/>
+    <mergeCell ref="L185:M185"/>
+    <mergeCell ref="R185:S185"/>
+    <mergeCell ref="L186:M186"/>
+    <mergeCell ref="R186:S186"/>
+    <mergeCell ref="R187:S187"/>
+    <mergeCell ref="L187:M187"/>
+    <mergeCell ref="L188:M188"/>
+    <mergeCell ref="L189:M189"/>
+    <mergeCell ref="L190:M190"/>
+    <mergeCell ref="L191:M191"/>
+    <mergeCell ref="L145:M145"/>
+    <mergeCell ref="L146:M146"/>
+    <mergeCell ref="L147:M147"/>
+    <mergeCell ref="L148:M148"/>
+    <mergeCell ref="L149:M149"/>
+    <mergeCell ref="L150:M150"/>
+    <mergeCell ref="L151:M151"/>
+    <mergeCell ref="L152:M152"/>
+    <mergeCell ref="L153:M153"/>
+    <mergeCell ref="L154:M154"/>
+    <mergeCell ref="L155:M155"/>
+    <mergeCell ref="L156:M156"/>
+    <mergeCell ref="L157:M157"/>
+    <mergeCell ref="L158:M158"/>
+    <mergeCell ref="L159:M159"/>
+    <mergeCell ref="L160:M160"/>
+    <mergeCell ref="L161:M161"/>
+    <mergeCell ref="L128:M128"/>
+    <mergeCell ref="L129:M129"/>
+    <mergeCell ref="L130:M130"/>
+    <mergeCell ref="L131:M131"/>
+    <mergeCell ref="L132:M132"/>
+    <mergeCell ref="L133:M133"/>
+    <mergeCell ref="L134:M134"/>
+    <mergeCell ref="L135:M135"/>
+    <mergeCell ref="L136:M136"/>
+    <mergeCell ref="L137:M137"/>
+    <mergeCell ref="L138:M138"/>
+    <mergeCell ref="L139:M139"/>
+    <mergeCell ref="L140:M140"/>
+    <mergeCell ref="L141:M141"/>
+    <mergeCell ref="L142:M142"/>
+    <mergeCell ref="L143:M143"/>
+    <mergeCell ref="L144:M144"/>
+    <mergeCell ref="R119:S119"/>
+    <mergeCell ref="R120:S120"/>
+    <mergeCell ref="R121:S121"/>
+    <mergeCell ref="R122:S122"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L116:M116"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="L118:M118"/>
+    <mergeCell ref="L119:M119"/>
+    <mergeCell ref="L120:M120"/>
+    <mergeCell ref="L121:M121"/>
+    <mergeCell ref="L122:M122"/>
+    <mergeCell ref="L123:M123"/>
+    <mergeCell ref="L124:M124"/>
+    <mergeCell ref="L125:M125"/>
+    <mergeCell ref="L126:M126"/>
+    <mergeCell ref="L127:M127"/>
+    <mergeCell ref="R102:S102"/>
+    <mergeCell ref="R103:S103"/>
+    <mergeCell ref="R104:S104"/>
+    <mergeCell ref="R105:S105"/>
+    <mergeCell ref="R106:S106"/>
+    <mergeCell ref="R107:S107"/>
+    <mergeCell ref="R108:S108"/>
+    <mergeCell ref="R109:S109"/>
+    <mergeCell ref="R110:S110"/>
+    <mergeCell ref="R111:S111"/>
+    <mergeCell ref="R112:S112"/>
+    <mergeCell ref="R113:S113"/>
+    <mergeCell ref="R114:S114"/>
+    <mergeCell ref="R115:S115"/>
+    <mergeCell ref="R116:S116"/>
+    <mergeCell ref="R117:S117"/>
+    <mergeCell ref="R118:S118"/>
+    <mergeCell ref="L111:M111"/>
+    <mergeCell ref="L112:M112"/>
+    <mergeCell ref="L113:M113"/>
+    <mergeCell ref="L114:M114"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="R76:S76"/>
+    <mergeCell ref="R77:S77"/>
+    <mergeCell ref="R78:S78"/>
+    <mergeCell ref="R79:S79"/>
+    <mergeCell ref="R80:S80"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="R82:S82"/>
+    <mergeCell ref="R83:S83"/>
+    <mergeCell ref="R84:S84"/>
+    <mergeCell ref="R85:S85"/>
+    <mergeCell ref="R86:S86"/>
+    <mergeCell ref="R87:S87"/>
+    <mergeCell ref="R88:S88"/>
+    <mergeCell ref="R89:S89"/>
+    <mergeCell ref="R90:S90"/>
+    <mergeCell ref="R91:S91"/>
+    <mergeCell ref="R92:S92"/>
+    <mergeCell ref="R93:S93"/>
+    <mergeCell ref="R94:S94"/>
+    <mergeCell ref="R95:S95"/>
+    <mergeCell ref="R96:S96"/>
+    <mergeCell ref="R97:S97"/>
+    <mergeCell ref="R98:S98"/>
+    <mergeCell ref="R99:S99"/>
+    <mergeCell ref="R100:S100"/>
+    <mergeCell ref="R101:S101"/>
+    <mergeCell ref="L94:M94"/>
+    <mergeCell ref="L95:M95"/>
+    <mergeCell ref="L96:M96"/>
+    <mergeCell ref="L97:M97"/>
+    <mergeCell ref="L98:M98"/>
+    <mergeCell ref="L99:M99"/>
+    <mergeCell ref="L100:M100"/>
+    <mergeCell ref="L101:M101"/>
+    <mergeCell ref="L102:M102"/>
+    <mergeCell ref="L103:M103"/>
+    <mergeCell ref="L104:M104"/>
+    <mergeCell ref="L105:M105"/>
+    <mergeCell ref="L106:M106"/>
+    <mergeCell ref="L107:M107"/>
+    <mergeCell ref="L108:M108"/>
+    <mergeCell ref="L109:M109"/>
+    <mergeCell ref="L110:M110"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="L78:M78"/>
+    <mergeCell ref="L79:M79"/>
+    <mergeCell ref="L80:M80"/>
+    <mergeCell ref="L81:M81"/>
+    <mergeCell ref="L82:M82"/>
+    <mergeCell ref="L83:M83"/>
+    <mergeCell ref="L84:M84"/>
+    <mergeCell ref="L85:M85"/>
+    <mergeCell ref="L86:M86"/>
+    <mergeCell ref="L87:M87"/>
+    <mergeCell ref="L88:M88"/>
+    <mergeCell ref="L89:M89"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L91:M91"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="L93:M93"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="L69:M69"/>
+    <mergeCell ref="L70:M70"/>
+    <mergeCell ref="L71:M71"/>
+    <mergeCell ref="L72:M72"/>
+    <mergeCell ref="L73:M73"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="L75:M75"/>
+    <mergeCell ref="L76:M76"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="R56:S56"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="R58:S58"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="R60:S60"/>
+    <mergeCell ref="R61:S61"/>
+    <mergeCell ref="R62:S62"/>
+    <mergeCell ref="R63:S63"/>
+    <mergeCell ref="R64:S64"/>
+    <mergeCell ref="R65:S65"/>
+    <mergeCell ref="R66:S66"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="L43:M43"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="R157:S157"/>
+    <mergeCell ref="R158:S158"/>
+    <mergeCell ref="R159:S159"/>
+    <mergeCell ref="R160:S160"/>
+    <mergeCell ref="R161:S161"/>
+    <mergeCell ref="R162:S162"/>
+    <mergeCell ref="R163:S163"/>
+    <mergeCell ref="R164:S164"/>
+    <mergeCell ref="R165:S165"/>
+    <mergeCell ref="R166:S166"/>
+    <mergeCell ref="R167:S167"/>
+    <mergeCell ref="R168:S168"/>
+    <mergeCell ref="R169:S169"/>
+    <mergeCell ref="R170:S170"/>
+    <mergeCell ref="R171:S171"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="R140:S140"/>
+    <mergeCell ref="R141:S141"/>
+    <mergeCell ref="R142:S142"/>
+    <mergeCell ref="R143:S143"/>
+    <mergeCell ref="R144:S144"/>
+    <mergeCell ref="R145:S145"/>
+    <mergeCell ref="R146:S146"/>
+    <mergeCell ref="R147:S147"/>
+    <mergeCell ref="R148:S148"/>
+    <mergeCell ref="R149:S149"/>
+    <mergeCell ref="R150:S150"/>
+    <mergeCell ref="R151:S151"/>
+    <mergeCell ref="R152:S152"/>
+    <mergeCell ref="R153:S153"/>
+    <mergeCell ref="R154:S154"/>
+    <mergeCell ref="R155:S155"/>
+    <mergeCell ref="R156:S156"/>
+    <mergeCell ref="R123:S123"/>
+    <mergeCell ref="R124:S124"/>
+    <mergeCell ref="R125:S125"/>
+    <mergeCell ref="R126:S126"/>
+    <mergeCell ref="R127:S127"/>
+    <mergeCell ref="R128:S128"/>
+    <mergeCell ref="R129:S129"/>
+    <mergeCell ref="R130:S130"/>
+    <mergeCell ref="R131:S131"/>
+    <mergeCell ref="R132:S132"/>
+    <mergeCell ref="R133:S133"/>
+    <mergeCell ref="R134:S134"/>
+    <mergeCell ref="R135:S135"/>
+    <mergeCell ref="R136:S136"/>
+    <mergeCell ref="R137:S137"/>
+    <mergeCell ref="R138:S138"/>
+    <mergeCell ref="R139:S139"/>
+    <mergeCell ref="L473:M473"/>
+    <mergeCell ref="L474:M474"/>
+    <mergeCell ref="L475:M475"/>
+    <mergeCell ref="R469:S469"/>
+    <mergeCell ref="R470:S470"/>
+    <mergeCell ref="L471:M471"/>
+    <mergeCell ref="R471:S471"/>
+    <mergeCell ref="L472:M472"/>
+    <mergeCell ref="R472:S472"/>
+    <mergeCell ref="R473:S473"/>
+    <mergeCell ref="R179:S179"/>
+    <mergeCell ref="R180:S180"/>
+    <mergeCell ref="R172:S172"/>
+    <mergeCell ref="R173:S173"/>
+    <mergeCell ref="R174:S174"/>
+    <mergeCell ref="R175:S175"/>
+    <mergeCell ref="R176:S176"/>
+    <mergeCell ref="R177:S177"/>
+    <mergeCell ref="R178:S178"/>
+    <mergeCell ref="L203:M203"/>
+    <mergeCell ref="L204:M204"/>
+    <mergeCell ref="L205:M205"/>
+    <mergeCell ref="L200:M200"/>
+    <mergeCell ref="R200:S200"/>
+    <mergeCell ref="L201:M201"/>
+    <mergeCell ref="R201:S201"/>
+    <mergeCell ref="L202:M202"/>
+    <mergeCell ref="R202:S202"/>
+    <mergeCell ref="R203:S203"/>
+    <mergeCell ref="L208:M208"/>
+    <mergeCell ref="L209:M209"/>
+    <mergeCell ref="L210:M210"/>
+    <mergeCell ref="L465:M465"/>
+    <mergeCell ref="R459:S459"/>
+    <mergeCell ref="R460:S460"/>
+    <mergeCell ref="L461:M461"/>
+    <mergeCell ref="R461:S461"/>
+    <mergeCell ref="L462:M462"/>
+    <mergeCell ref="R462:S462"/>
+    <mergeCell ref="R463:S463"/>
+    <mergeCell ref="L468:M468"/>
+    <mergeCell ref="L469:M469"/>
+    <mergeCell ref="L470:M470"/>
+    <mergeCell ref="R464:S464"/>
+    <mergeCell ref="R465:S465"/>
+    <mergeCell ref="L466:M466"/>
+    <mergeCell ref="R466:S466"/>
+    <mergeCell ref="L467:M467"/>
+    <mergeCell ref="R467:S467"/>
+    <mergeCell ref="R468:S468"/>
+    <mergeCell ref="L507:M507"/>
+    <mergeCell ref="R507:S507"/>
+    <mergeCell ref="L508:M508"/>
+    <mergeCell ref="R508:S508"/>
+    <mergeCell ref="L443:M443"/>
+    <mergeCell ref="L444:M444"/>
+    <mergeCell ref="L445:M445"/>
+    <mergeCell ref="R439:S439"/>
+    <mergeCell ref="R440:S440"/>
+    <mergeCell ref="L441:M441"/>
+    <mergeCell ref="R441:S441"/>
+    <mergeCell ref="L442:M442"/>
+    <mergeCell ref="R442:S442"/>
+    <mergeCell ref="R443:S443"/>
+    <mergeCell ref="L448:M448"/>
+    <mergeCell ref="L449:M449"/>
+    <mergeCell ref="L450:M450"/>
+    <mergeCell ref="R444:S444"/>
+    <mergeCell ref="R445:S445"/>
+    <mergeCell ref="L446:M446"/>
+    <mergeCell ref="R446:S446"/>
+    <mergeCell ref="L447:M447"/>
+    <mergeCell ref="R447:S447"/>
+    <mergeCell ref="R448:S448"/>
+    <mergeCell ref="L453:M453"/>
+    <mergeCell ref="L454:M454"/>
+    <mergeCell ref="L455:M455"/>
+    <mergeCell ref="R449:S449"/>
+    <mergeCell ref="R450:S450"/>
+    <mergeCell ref="L451:M451"/>
+    <mergeCell ref="R451:S451"/>
+    <mergeCell ref="L452:M452"/>
     <mergeCell ref="L192:M192"/>
     <mergeCell ref="L193:M193"/>
     <mergeCell ref="R504:S504"/>
@@ -15446,779 +16008,217 @@
     <mergeCell ref="R498:S498"/>
     <mergeCell ref="L503:M503"/>
     <mergeCell ref="L504:M504"/>
-    <mergeCell ref="L507:M507"/>
-    <mergeCell ref="R507:S507"/>
-    <mergeCell ref="L508:M508"/>
-    <mergeCell ref="R508:S508"/>
-    <mergeCell ref="L443:M443"/>
-    <mergeCell ref="L444:M444"/>
-    <mergeCell ref="L445:M445"/>
-    <mergeCell ref="R439:S439"/>
-    <mergeCell ref="R440:S440"/>
-    <mergeCell ref="L441:M441"/>
-    <mergeCell ref="R441:S441"/>
-    <mergeCell ref="L442:M442"/>
-    <mergeCell ref="R442:S442"/>
-    <mergeCell ref="R443:S443"/>
-    <mergeCell ref="L448:M448"/>
-    <mergeCell ref="L449:M449"/>
-    <mergeCell ref="L450:M450"/>
-    <mergeCell ref="R444:S444"/>
-    <mergeCell ref="R445:S445"/>
-    <mergeCell ref="L446:M446"/>
-    <mergeCell ref="R446:S446"/>
-    <mergeCell ref="L447:M447"/>
-    <mergeCell ref="R447:S447"/>
-    <mergeCell ref="R448:S448"/>
-    <mergeCell ref="L453:M453"/>
-    <mergeCell ref="L454:M454"/>
-    <mergeCell ref="L455:M455"/>
-    <mergeCell ref="R449:S449"/>
-    <mergeCell ref="R450:S450"/>
-    <mergeCell ref="L451:M451"/>
-    <mergeCell ref="R451:S451"/>
-    <mergeCell ref="L452:M452"/>
-    <mergeCell ref="L465:M465"/>
-    <mergeCell ref="R459:S459"/>
-    <mergeCell ref="R460:S460"/>
-    <mergeCell ref="L461:M461"/>
-    <mergeCell ref="R461:S461"/>
-    <mergeCell ref="L462:M462"/>
-    <mergeCell ref="R462:S462"/>
-    <mergeCell ref="R463:S463"/>
-    <mergeCell ref="L468:M468"/>
-    <mergeCell ref="L469:M469"/>
-    <mergeCell ref="L470:M470"/>
-    <mergeCell ref="R464:S464"/>
-    <mergeCell ref="R465:S465"/>
-    <mergeCell ref="L466:M466"/>
-    <mergeCell ref="R466:S466"/>
-    <mergeCell ref="L467:M467"/>
-    <mergeCell ref="R467:S467"/>
-    <mergeCell ref="R468:S468"/>
-    <mergeCell ref="L473:M473"/>
-    <mergeCell ref="L474:M474"/>
-    <mergeCell ref="L475:M475"/>
-    <mergeCell ref="R469:S469"/>
-    <mergeCell ref="R470:S470"/>
-    <mergeCell ref="L471:M471"/>
-    <mergeCell ref="R471:S471"/>
-    <mergeCell ref="L472:M472"/>
-    <mergeCell ref="R472:S472"/>
-    <mergeCell ref="R473:S473"/>
-    <mergeCell ref="R179:S179"/>
-    <mergeCell ref="R180:S180"/>
-    <mergeCell ref="R172:S172"/>
-    <mergeCell ref="R173:S173"/>
-    <mergeCell ref="R174:S174"/>
-    <mergeCell ref="R175:S175"/>
-    <mergeCell ref="R176:S176"/>
-    <mergeCell ref="R177:S177"/>
-    <mergeCell ref="R178:S178"/>
-    <mergeCell ref="L203:M203"/>
-    <mergeCell ref="L204:M204"/>
-    <mergeCell ref="L205:M205"/>
-    <mergeCell ref="L200:M200"/>
-    <mergeCell ref="R200:S200"/>
-    <mergeCell ref="L201:M201"/>
-    <mergeCell ref="R201:S201"/>
-    <mergeCell ref="L202:M202"/>
-    <mergeCell ref="R202:S202"/>
-    <mergeCell ref="R203:S203"/>
-    <mergeCell ref="L208:M208"/>
-    <mergeCell ref="L209:M209"/>
-    <mergeCell ref="L210:M210"/>
-    <mergeCell ref="R144:S144"/>
-    <mergeCell ref="R145:S145"/>
-    <mergeCell ref="R146:S146"/>
-    <mergeCell ref="R147:S147"/>
-    <mergeCell ref="R148:S148"/>
-    <mergeCell ref="R149:S149"/>
-    <mergeCell ref="R150:S150"/>
-    <mergeCell ref="R151:S151"/>
-    <mergeCell ref="R152:S152"/>
-    <mergeCell ref="R153:S153"/>
-    <mergeCell ref="R154:S154"/>
-    <mergeCell ref="R155:S155"/>
-    <mergeCell ref="R156:S156"/>
-    <mergeCell ref="R123:S123"/>
-    <mergeCell ref="R124:S124"/>
-    <mergeCell ref="R125:S125"/>
-    <mergeCell ref="R126:S126"/>
-    <mergeCell ref="R127:S127"/>
-    <mergeCell ref="R128:S128"/>
-    <mergeCell ref="R129:S129"/>
-    <mergeCell ref="R130:S130"/>
-    <mergeCell ref="R131:S131"/>
-    <mergeCell ref="R132:S132"/>
-    <mergeCell ref="R133:S133"/>
-    <mergeCell ref="R134:S134"/>
-    <mergeCell ref="R135:S135"/>
-    <mergeCell ref="R136:S136"/>
-    <mergeCell ref="R137:S137"/>
-    <mergeCell ref="R138:S138"/>
-    <mergeCell ref="R139:S139"/>
-    <mergeCell ref="R157:S157"/>
-    <mergeCell ref="R158:S158"/>
-    <mergeCell ref="R159:S159"/>
-    <mergeCell ref="R160:S160"/>
-    <mergeCell ref="R161:S161"/>
-    <mergeCell ref="R162:S162"/>
-    <mergeCell ref="R163:S163"/>
-    <mergeCell ref="R164:S164"/>
-    <mergeCell ref="R165:S165"/>
-    <mergeCell ref="R166:S166"/>
-    <mergeCell ref="R167:S167"/>
-    <mergeCell ref="R168:S168"/>
-    <mergeCell ref="R169:S169"/>
-    <mergeCell ref="R170:S170"/>
-    <mergeCell ref="R171:S171"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="R140:S140"/>
-    <mergeCell ref="R141:S141"/>
-    <mergeCell ref="R142:S142"/>
-    <mergeCell ref="R143:S143"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="L42:M42"/>
-    <mergeCell ref="L43:M43"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="R55:S55"/>
-    <mergeCell ref="R56:S56"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="R58:S58"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="R60:S60"/>
-    <mergeCell ref="R61:S61"/>
-    <mergeCell ref="R62:S62"/>
-    <mergeCell ref="R63:S63"/>
-    <mergeCell ref="R64:S64"/>
-    <mergeCell ref="R65:S65"/>
-    <mergeCell ref="R66:S66"/>
-    <mergeCell ref="R67:S67"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="L69:M69"/>
-    <mergeCell ref="L70:M70"/>
-    <mergeCell ref="L71:M71"/>
-    <mergeCell ref="L72:M72"/>
-    <mergeCell ref="L73:M73"/>
-    <mergeCell ref="L74:M74"/>
-    <mergeCell ref="L75:M75"/>
-    <mergeCell ref="L76:M76"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="L78:M78"/>
-    <mergeCell ref="L79:M79"/>
-    <mergeCell ref="L80:M80"/>
-    <mergeCell ref="L81:M81"/>
-    <mergeCell ref="L82:M82"/>
-    <mergeCell ref="L83:M83"/>
-    <mergeCell ref="L84:M84"/>
-    <mergeCell ref="L85:M85"/>
-    <mergeCell ref="L86:M86"/>
-    <mergeCell ref="L87:M87"/>
-    <mergeCell ref="L88:M88"/>
-    <mergeCell ref="L89:M89"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L91:M91"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="L93:M93"/>
-    <mergeCell ref="L94:M94"/>
-    <mergeCell ref="L95:M95"/>
-    <mergeCell ref="L96:M96"/>
-    <mergeCell ref="L97:M97"/>
-    <mergeCell ref="L98:M98"/>
-    <mergeCell ref="L99:M99"/>
-    <mergeCell ref="L100:M100"/>
-    <mergeCell ref="L101:M101"/>
-    <mergeCell ref="L102:M102"/>
-    <mergeCell ref="L103:M103"/>
-    <mergeCell ref="L104:M104"/>
-    <mergeCell ref="L105:M105"/>
-    <mergeCell ref="L106:M106"/>
-    <mergeCell ref="L107:M107"/>
-    <mergeCell ref="L108:M108"/>
-    <mergeCell ref="L109:M109"/>
-    <mergeCell ref="L110:M110"/>
-    <mergeCell ref="L111:M111"/>
-    <mergeCell ref="L112:M112"/>
-    <mergeCell ref="L113:M113"/>
-    <mergeCell ref="L114:M114"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="R76:S76"/>
-    <mergeCell ref="R77:S77"/>
-    <mergeCell ref="R78:S78"/>
-    <mergeCell ref="R79:S79"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="R82:S82"/>
-    <mergeCell ref="R83:S83"/>
-    <mergeCell ref="R84:S84"/>
-    <mergeCell ref="R85:S85"/>
-    <mergeCell ref="R86:S86"/>
-    <mergeCell ref="R87:S87"/>
-    <mergeCell ref="R88:S88"/>
-    <mergeCell ref="R89:S89"/>
-    <mergeCell ref="R90:S90"/>
-    <mergeCell ref="R91:S91"/>
-    <mergeCell ref="R92:S92"/>
-    <mergeCell ref="R93:S93"/>
-    <mergeCell ref="R94:S94"/>
-    <mergeCell ref="R95:S95"/>
-    <mergeCell ref="R96:S96"/>
-    <mergeCell ref="R97:S97"/>
-    <mergeCell ref="R98:S98"/>
-    <mergeCell ref="R99:S99"/>
-    <mergeCell ref="R100:S100"/>
-    <mergeCell ref="R101:S101"/>
-    <mergeCell ref="R102:S102"/>
-    <mergeCell ref="R103:S103"/>
-    <mergeCell ref="R104:S104"/>
-    <mergeCell ref="R105:S105"/>
-    <mergeCell ref="R106:S106"/>
-    <mergeCell ref="R107:S107"/>
-    <mergeCell ref="R108:S108"/>
-    <mergeCell ref="R109:S109"/>
-    <mergeCell ref="R110:S110"/>
-    <mergeCell ref="R111:S111"/>
-    <mergeCell ref="R112:S112"/>
-    <mergeCell ref="R113:S113"/>
-    <mergeCell ref="R114:S114"/>
-    <mergeCell ref="R115:S115"/>
-    <mergeCell ref="R116:S116"/>
-    <mergeCell ref="R117:S117"/>
-    <mergeCell ref="R118:S118"/>
-    <mergeCell ref="R119:S119"/>
-    <mergeCell ref="R120:S120"/>
-    <mergeCell ref="R121:S121"/>
-    <mergeCell ref="R122:S122"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L116:M116"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="L118:M118"/>
-    <mergeCell ref="L119:M119"/>
-    <mergeCell ref="L120:M120"/>
-    <mergeCell ref="L121:M121"/>
-    <mergeCell ref="L122:M122"/>
-    <mergeCell ref="L123:M123"/>
-    <mergeCell ref="L124:M124"/>
-    <mergeCell ref="L125:M125"/>
-    <mergeCell ref="L126:M126"/>
-    <mergeCell ref="L127:M127"/>
-    <mergeCell ref="L128:M128"/>
-    <mergeCell ref="L129:M129"/>
-    <mergeCell ref="L130:M130"/>
-    <mergeCell ref="L131:M131"/>
-    <mergeCell ref="L132:M132"/>
-    <mergeCell ref="L133:M133"/>
-    <mergeCell ref="L134:M134"/>
-    <mergeCell ref="L135:M135"/>
-    <mergeCell ref="L136:M136"/>
-    <mergeCell ref="L137:M137"/>
-    <mergeCell ref="L138:M138"/>
-    <mergeCell ref="L139:M139"/>
-    <mergeCell ref="L140:M140"/>
-    <mergeCell ref="L141:M141"/>
-    <mergeCell ref="L142:M142"/>
-    <mergeCell ref="L143:M143"/>
-    <mergeCell ref="L144:M144"/>
-    <mergeCell ref="L145:M145"/>
-    <mergeCell ref="L146:M146"/>
-    <mergeCell ref="L147:M147"/>
-    <mergeCell ref="L148:M148"/>
-    <mergeCell ref="L149:M149"/>
-    <mergeCell ref="L150:M150"/>
-    <mergeCell ref="L151:M151"/>
-    <mergeCell ref="L152:M152"/>
-    <mergeCell ref="L153:M153"/>
-    <mergeCell ref="L154:M154"/>
-    <mergeCell ref="L155:M155"/>
-    <mergeCell ref="L156:M156"/>
-    <mergeCell ref="L157:M157"/>
-    <mergeCell ref="L158:M158"/>
-    <mergeCell ref="L159:M159"/>
-    <mergeCell ref="L160:M160"/>
-    <mergeCell ref="L161:M161"/>
-    <mergeCell ref="L162:M162"/>
-    <mergeCell ref="L163:M163"/>
-    <mergeCell ref="R195:S195"/>
-    <mergeCell ref="R196:S196"/>
-    <mergeCell ref="R188:S188"/>
-    <mergeCell ref="R189:S189"/>
-    <mergeCell ref="R190:S190"/>
-    <mergeCell ref="R191:S191"/>
-    <mergeCell ref="R192:S192"/>
-    <mergeCell ref="R193:S193"/>
-    <mergeCell ref="R194:S194"/>
-    <mergeCell ref="R198:S198"/>
-    <mergeCell ref="R199:S199"/>
-    <mergeCell ref="L194:M194"/>
-    <mergeCell ref="L195:M195"/>
-    <mergeCell ref="L196:M196"/>
-    <mergeCell ref="L197:M197"/>
-    <mergeCell ref="R197:S197"/>
-    <mergeCell ref="L198:M198"/>
-    <mergeCell ref="L199:M199"/>
-    <mergeCell ref="L184:M184"/>
-    <mergeCell ref="R184:S184"/>
-    <mergeCell ref="L185:M185"/>
-    <mergeCell ref="R185:S185"/>
-    <mergeCell ref="L186:M186"/>
-    <mergeCell ref="R186:S186"/>
-    <mergeCell ref="R187:S187"/>
-    <mergeCell ref="L187:M187"/>
-    <mergeCell ref="L188:M188"/>
-    <mergeCell ref="L189:M189"/>
-    <mergeCell ref="L190:M190"/>
-    <mergeCell ref="L191:M191"/>
-    <mergeCell ref="R204:S204"/>
-    <mergeCell ref="R205:S205"/>
-    <mergeCell ref="L206:M206"/>
-    <mergeCell ref="R206:S206"/>
-    <mergeCell ref="L207:M207"/>
-    <mergeCell ref="R207:S207"/>
-    <mergeCell ref="R208:S208"/>
-    <mergeCell ref="L213:M213"/>
-    <mergeCell ref="L214:M214"/>
-    <mergeCell ref="L215:M215"/>
-    <mergeCell ref="R209:S209"/>
-    <mergeCell ref="R210:S210"/>
-    <mergeCell ref="L211:M211"/>
-    <mergeCell ref="R211:S211"/>
-    <mergeCell ref="L212:M212"/>
-    <mergeCell ref="R212:S212"/>
-    <mergeCell ref="R213:S213"/>
-    <mergeCell ref="L218:M218"/>
-    <mergeCell ref="L219:M219"/>
-    <mergeCell ref="L220:M220"/>
-    <mergeCell ref="R214:S214"/>
-    <mergeCell ref="R215:S215"/>
-    <mergeCell ref="L216:M216"/>
-    <mergeCell ref="R216:S216"/>
-    <mergeCell ref="L217:M217"/>
-    <mergeCell ref="R217:S217"/>
-    <mergeCell ref="R218:S218"/>
-    <mergeCell ref="L223:M223"/>
-    <mergeCell ref="L224:M224"/>
-    <mergeCell ref="L225:M225"/>
-    <mergeCell ref="R219:S219"/>
-    <mergeCell ref="R220:S220"/>
-    <mergeCell ref="L221:M221"/>
-    <mergeCell ref="R221:S221"/>
-    <mergeCell ref="L222:M222"/>
-    <mergeCell ref="R222:S222"/>
-    <mergeCell ref="R223:S223"/>
-    <mergeCell ref="L228:M228"/>
-    <mergeCell ref="L229:M229"/>
-    <mergeCell ref="L230:M230"/>
-    <mergeCell ref="R224:S224"/>
-    <mergeCell ref="R225:S225"/>
-    <mergeCell ref="L226:M226"/>
-    <mergeCell ref="R226:S226"/>
-    <mergeCell ref="L227:M227"/>
-    <mergeCell ref="R227:S227"/>
-    <mergeCell ref="R228:S228"/>
-    <mergeCell ref="L233:M233"/>
-    <mergeCell ref="L234:M234"/>
-    <mergeCell ref="L235:M235"/>
-    <mergeCell ref="R229:S229"/>
-    <mergeCell ref="R230:S230"/>
-    <mergeCell ref="L231:M231"/>
-    <mergeCell ref="R231:S231"/>
-    <mergeCell ref="L232:M232"/>
-    <mergeCell ref="R232:S232"/>
-    <mergeCell ref="R233:S233"/>
-    <mergeCell ref="L238:M238"/>
-    <mergeCell ref="L239:M239"/>
-    <mergeCell ref="L240:M240"/>
-    <mergeCell ref="R234:S234"/>
-    <mergeCell ref="R235:S235"/>
-    <mergeCell ref="L236:M236"/>
-    <mergeCell ref="R236:S236"/>
-    <mergeCell ref="L237:M237"/>
-    <mergeCell ref="R237:S237"/>
-    <mergeCell ref="R238:S238"/>
-    <mergeCell ref="L243:M243"/>
-    <mergeCell ref="L244:M244"/>
-    <mergeCell ref="L245:M245"/>
-    <mergeCell ref="R239:S239"/>
-    <mergeCell ref="R240:S240"/>
-    <mergeCell ref="L241:M241"/>
-    <mergeCell ref="R241:S241"/>
-    <mergeCell ref="L242:M242"/>
-    <mergeCell ref="R242:S242"/>
-    <mergeCell ref="R243:S243"/>
-    <mergeCell ref="L248:M248"/>
-    <mergeCell ref="L249:M249"/>
-    <mergeCell ref="L250:M250"/>
-    <mergeCell ref="R244:S244"/>
-    <mergeCell ref="R245:S245"/>
-    <mergeCell ref="L246:M246"/>
-    <mergeCell ref="R246:S246"/>
-    <mergeCell ref="L247:M247"/>
-    <mergeCell ref="R247:S247"/>
-    <mergeCell ref="R248:S248"/>
-    <mergeCell ref="L253:M253"/>
-    <mergeCell ref="L254:M254"/>
-    <mergeCell ref="L255:M255"/>
-    <mergeCell ref="R249:S249"/>
-    <mergeCell ref="R250:S250"/>
-    <mergeCell ref="L251:M251"/>
-    <mergeCell ref="R251:S251"/>
-    <mergeCell ref="L252:M252"/>
-    <mergeCell ref="R252:S252"/>
-    <mergeCell ref="R253:S253"/>
-    <mergeCell ref="L258:M258"/>
-    <mergeCell ref="L259:M259"/>
-    <mergeCell ref="L260:M260"/>
-    <mergeCell ref="R254:S254"/>
-    <mergeCell ref="R255:S255"/>
-    <mergeCell ref="L256:M256"/>
-    <mergeCell ref="R256:S256"/>
-    <mergeCell ref="L257:M257"/>
-    <mergeCell ref="R257:S257"/>
-    <mergeCell ref="R258:S258"/>
-    <mergeCell ref="L263:M263"/>
-    <mergeCell ref="L264:M264"/>
-    <mergeCell ref="L265:M265"/>
-    <mergeCell ref="R259:S259"/>
-    <mergeCell ref="R260:S260"/>
-    <mergeCell ref="L261:M261"/>
-    <mergeCell ref="R261:S261"/>
-    <mergeCell ref="L262:M262"/>
-    <mergeCell ref="R262:S262"/>
-    <mergeCell ref="R263:S263"/>
-    <mergeCell ref="L268:M268"/>
-    <mergeCell ref="L269:M269"/>
-    <mergeCell ref="L270:M270"/>
-    <mergeCell ref="R264:S264"/>
-    <mergeCell ref="R265:S265"/>
-    <mergeCell ref="L266:M266"/>
-    <mergeCell ref="R266:S266"/>
-    <mergeCell ref="L267:M267"/>
-    <mergeCell ref="R267:S267"/>
-    <mergeCell ref="R268:S268"/>
-    <mergeCell ref="L273:M273"/>
-    <mergeCell ref="L274:M274"/>
-    <mergeCell ref="L275:M275"/>
-    <mergeCell ref="R269:S269"/>
-    <mergeCell ref="R270:S270"/>
-    <mergeCell ref="L271:M271"/>
-    <mergeCell ref="R271:S271"/>
-    <mergeCell ref="L272:M272"/>
-    <mergeCell ref="R272:S272"/>
-    <mergeCell ref="R273:S273"/>
-    <mergeCell ref="L278:M278"/>
-    <mergeCell ref="L279:M279"/>
-    <mergeCell ref="L280:M280"/>
-    <mergeCell ref="R274:S274"/>
-    <mergeCell ref="R275:S275"/>
-    <mergeCell ref="L276:M276"/>
-    <mergeCell ref="R276:S276"/>
-    <mergeCell ref="L277:M277"/>
-    <mergeCell ref="R277:S277"/>
-    <mergeCell ref="R278:S278"/>
-    <mergeCell ref="L283:M283"/>
-    <mergeCell ref="L284:M284"/>
-    <mergeCell ref="L285:M285"/>
-    <mergeCell ref="R279:S279"/>
-    <mergeCell ref="R280:S280"/>
-    <mergeCell ref="L281:M281"/>
-    <mergeCell ref="R281:S281"/>
-    <mergeCell ref="L282:M282"/>
-    <mergeCell ref="R282:S282"/>
-    <mergeCell ref="R283:S283"/>
-    <mergeCell ref="L288:M288"/>
-    <mergeCell ref="L289:M289"/>
-    <mergeCell ref="L290:M290"/>
-    <mergeCell ref="R284:S284"/>
-    <mergeCell ref="R285:S285"/>
-    <mergeCell ref="L286:M286"/>
-    <mergeCell ref="R286:S286"/>
-    <mergeCell ref="L287:M287"/>
-    <mergeCell ref="R287:S287"/>
-    <mergeCell ref="R288:S288"/>
-    <mergeCell ref="L293:M293"/>
-    <mergeCell ref="L294:M294"/>
-    <mergeCell ref="L295:M295"/>
-    <mergeCell ref="R289:S289"/>
-    <mergeCell ref="R290:S290"/>
-    <mergeCell ref="L291:M291"/>
-    <mergeCell ref="R291:S291"/>
-    <mergeCell ref="L292:M292"/>
-    <mergeCell ref="R292:S292"/>
-    <mergeCell ref="R293:S293"/>
-    <mergeCell ref="L298:M298"/>
-    <mergeCell ref="L299:M299"/>
-    <mergeCell ref="L300:M300"/>
-    <mergeCell ref="R294:S294"/>
-    <mergeCell ref="R295:S295"/>
-    <mergeCell ref="L296:M296"/>
-    <mergeCell ref="R296:S296"/>
-    <mergeCell ref="L297:M297"/>
-    <mergeCell ref="R297:S297"/>
-    <mergeCell ref="R298:S298"/>
-    <mergeCell ref="L303:M303"/>
-    <mergeCell ref="L304:M304"/>
-    <mergeCell ref="L305:M305"/>
-    <mergeCell ref="R299:S299"/>
-    <mergeCell ref="R300:S300"/>
-    <mergeCell ref="L301:M301"/>
-    <mergeCell ref="R301:S301"/>
-    <mergeCell ref="L302:M302"/>
-    <mergeCell ref="R302:S302"/>
-    <mergeCell ref="R303:S303"/>
-    <mergeCell ref="L308:M308"/>
-    <mergeCell ref="L309:M309"/>
-    <mergeCell ref="L310:M310"/>
-    <mergeCell ref="R304:S304"/>
-    <mergeCell ref="R305:S305"/>
-    <mergeCell ref="L306:M306"/>
-    <mergeCell ref="R306:S306"/>
-    <mergeCell ref="L307:M307"/>
-    <mergeCell ref="R307:S307"/>
-    <mergeCell ref="R308:S308"/>
-    <mergeCell ref="L313:M313"/>
-    <mergeCell ref="L314:M314"/>
-    <mergeCell ref="L315:M315"/>
-    <mergeCell ref="R309:S309"/>
-    <mergeCell ref="R310:S310"/>
-    <mergeCell ref="L311:M311"/>
-    <mergeCell ref="R311:S311"/>
-    <mergeCell ref="L312:M312"/>
-    <mergeCell ref="R312:S312"/>
-    <mergeCell ref="R313:S313"/>
-    <mergeCell ref="L318:M318"/>
-    <mergeCell ref="L319:M319"/>
-    <mergeCell ref="L320:M320"/>
-    <mergeCell ref="R314:S314"/>
-    <mergeCell ref="R315:S315"/>
-    <mergeCell ref="L316:M316"/>
-    <mergeCell ref="R316:S316"/>
-    <mergeCell ref="L317:M317"/>
-    <mergeCell ref="R317:S317"/>
-    <mergeCell ref="R318:S318"/>
-    <mergeCell ref="L323:M323"/>
-    <mergeCell ref="L324:M324"/>
-    <mergeCell ref="L325:M325"/>
-    <mergeCell ref="R319:S319"/>
-    <mergeCell ref="R320:S320"/>
-    <mergeCell ref="L321:M321"/>
-    <mergeCell ref="R321:S321"/>
-    <mergeCell ref="L322:M322"/>
-    <mergeCell ref="R322:S322"/>
-    <mergeCell ref="R323:S323"/>
-    <mergeCell ref="L328:M328"/>
-    <mergeCell ref="L329:M329"/>
-    <mergeCell ref="L330:M330"/>
-    <mergeCell ref="R324:S324"/>
-    <mergeCell ref="R325:S325"/>
-    <mergeCell ref="L326:M326"/>
-    <mergeCell ref="R326:S326"/>
-    <mergeCell ref="L327:M327"/>
-    <mergeCell ref="R327:S327"/>
-    <mergeCell ref="R328:S328"/>
-    <mergeCell ref="L333:M333"/>
-    <mergeCell ref="L334:M334"/>
-    <mergeCell ref="L335:M335"/>
-    <mergeCell ref="R329:S329"/>
-    <mergeCell ref="R330:S330"/>
-    <mergeCell ref="L331:M331"/>
-    <mergeCell ref="R331:S331"/>
-    <mergeCell ref="L332:M332"/>
-    <mergeCell ref="R332:S332"/>
-    <mergeCell ref="R333:S333"/>
-    <mergeCell ref="L338:M338"/>
-    <mergeCell ref="L339:M339"/>
-    <mergeCell ref="L340:M340"/>
-    <mergeCell ref="R334:S334"/>
-    <mergeCell ref="R335:S335"/>
-    <mergeCell ref="L336:M336"/>
-    <mergeCell ref="R336:S336"/>
-    <mergeCell ref="L337:M337"/>
-    <mergeCell ref="R337:S337"/>
-    <mergeCell ref="R338:S338"/>
-    <mergeCell ref="L343:M343"/>
-    <mergeCell ref="L344:M344"/>
-    <mergeCell ref="L345:M345"/>
-    <mergeCell ref="R339:S339"/>
-    <mergeCell ref="R340:S340"/>
-    <mergeCell ref="L341:M341"/>
-    <mergeCell ref="R341:S341"/>
-    <mergeCell ref="L342:M342"/>
-    <mergeCell ref="R342:S342"/>
-    <mergeCell ref="R343:S343"/>
-    <mergeCell ref="L348:M348"/>
-    <mergeCell ref="L349:M349"/>
-    <mergeCell ref="L350:M350"/>
-    <mergeCell ref="R344:S344"/>
-    <mergeCell ref="R345:S345"/>
-    <mergeCell ref="L346:M346"/>
-    <mergeCell ref="R346:S346"/>
-    <mergeCell ref="L347:M347"/>
-    <mergeCell ref="R347:S347"/>
-    <mergeCell ref="R348:S348"/>
-    <mergeCell ref="L353:M353"/>
-    <mergeCell ref="L354:M354"/>
-    <mergeCell ref="L355:M355"/>
-    <mergeCell ref="R349:S349"/>
-    <mergeCell ref="R350:S350"/>
-    <mergeCell ref="L351:M351"/>
-    <mergeCell ref="R351:S351"/>
-    <mergeCell ref="L352:M352"/>
-    <mergeCell ref="R352:S352"/>
-    <mergeCell ref="R353:S353"/>
-    <mergeCell ref="L368:M368"/>
-    <mergeCell ref="L369:M369"/>
-    <mergeCell ref="L370:M370"/>
-    <mergeCell ref="R364:S364"/>
-    <mergeCell ref="R365:S365"/>
-    <mergeCell ref="L366:M366"/>
-    <mergeCell ref="R366:S366"/>
-    <mergeCell ref="L367:M367"/>
-    <mergeCell ref="R367:S367"/>
-    <mergeCell ref="R368:S368"/>
-    <mergeCell ref="L358:M358"/>
-    <mergeCell ref="L359:M359"/>
-    <mergeCell ref="L360:M360"/>
-    <mergeCell ref="R354:S354"/>
-    <mergeCell ref="R355:S355"/>
-    <mergeCell ref="L356:M356"/>
-    <mergeCell ref="R356:S356"/>
-    <mergeCell ref="L357:M357"/>
-    <mergeCell ref="R357:S357"/>
-    <mergeCell ref="R358:S358"/>
-    <mergeCell ref="L363:M363"/>
-    <mergeCell ref="L364:M364"/>
-    <mergeCell ref="L365:M365"/>
-    <mergeCell ref="R359:S359"/>
-    <mergeCell ref="R360:S360"/>
-    <mergeCell ref="L361:M361"/>
-    <mergeCell ref="R361:S361"/>
-    <mergeCell ref="L362:M362"/>
-    <mergeCell ref="R362:S362"/>
-    <mergeCell ref="R363:S363"/>
+    <mergeCell ref="L164:M164"/>
+    <mergeCell ref="L165:M165"/>
+    <mergeCell ref="L166:M166"/>
+    <mergeCell ref="L167:M167"/>
+    <mergeCell ref="L168:M168"/>
+    <mergeCell ref="L169:M169"/>
+    <mergeCell ref="L170:M170"/>
+    <mergeCell ref="L171:M171"/>
+    <mergeCell ref="L172:M172"/>
+    <mergeCell ref="L173:M173"/>
+    <mergeCell ref="L174:M174"/>
+    <mergeCell ref="L175:M175"/>
+    <mergeCell ref="L176:M176"/>
+    <mergeCell ref="L177:M177"/>
+    <mergeCell ref="R182:S182"/>
+    <mergeCell ref="R183:S183"/>
+    <mergeCell ref="L178:M178"/>
+    <mergeCell ref="L179:M179"/>
+    <mergeCell ref="L180:M180"/>
+    <mergeCell ref="L181:M181"/>
+    <mergeCell ref="R181:S181"/>
+    <mergeCell ref="L182:M182"/>
+    <mergeCell ref="L183:M183"/>
+    <mergeCell ref="L505:M505"/>
+    <mergeCell ref="R499:S499"/>
+    <mergeCell ref="R500:S500"/>
+    <mergeCell ref="L501:M501"/>
+    <mergeCell ref="R501:S501"/>
+    <mergeCell ref="L502:M502"/>
+    <mergeCell ref="R502:S502"/>
+    <mergeCell ref="R503:S503"/>
+    <mergeCell ref="L488:M488"/>
+    <mergeCell ref="L489:M489"/>
+    <mergeCell ref="L490:M490"/>
+    <mergeCell ref="R484:S484"/>
+    <mergeCell ref="R485:S485"/>
+    <mergeCell ref="L486:M486"/>
+    <mergeCell ref="R486:S486"/>
+    <mergeCell ref="L487:M487"/>
+    <mergeCell ref="R487:S487"/>
+    <mergeCell ref="R488:S488"/>
+    <mergeCell ref="L493:M493"/>
+    <mergeCell ref="L494:M494"/>
+    <mergeCell ref="L495:M495"/>
+    <mergeCell ref="R489:S489"/>
+    <mergeCell ref="R490:S490"/>
+    <mergeCell ref="L491:M491"/>
+    <mergeCell ref="R491:S491"/>
+    <mergeCell ref="L492:M492"/>
+    <mergeCell ref="R492:S492"/>
+    <mergeCell ref="R493:S493"/>
+    <mergeCell ref="L478:M478"/>
+    <mergeCell ref="L479:M479"/>
+    <mergeCell ref="L480:M480"/>
+    <mergeCell ref="R474:S474"/>
+    <mergeCell ref="R475:S475"/>
+    <mergeCell ref="L476:M476"/>
+    <mergeCell ref="R476:S476"/>
+    <mergeCell ref="L477:M477"/>
+    <mergeCell ref="R477:S477"/>
+    <mergeCell ref="R478:S478"/>
+    <mergeCell ref="L483:M483"/>
+    <mergeCell ref="L484:M484"/>
+    <mergeCell ref="L485:M485"/>
+    <mergeCell ref="R479:S479"/>
+    <mergeCell ref="R480:S480"/>
+    <mergeCell ref="L481:M481"/>
+    <mergeCell ref="R481:S481"/>
+    <mergeCell ref="L482:M482"/>
+    <mergeCell ref="R482:S482"/>
+    <mergeCell ref="R483:S483"/>
+    <mergeCell ref="L433:M433"/>
+    <mergeCell ref="L434:M434"/>
+    <mergeCell ref="L435:M435"/>
+    <mergeCell ref="R429:S429"/>
+    <mergeCell ref="R430:S430"/>
+    <mergeCell ref="L431:M431"/>
+    <mergeCell ref="R431:S431"/>
+    <mergeCell ref="L432:M432"/>
+    <mergeCell ref="R432:S432"/>
+    <mergeCell ref="R433:S433"/>
+    <mergeCell ref="L438:M438"/>
+    <mergeCell ref="L439:M439"/>
+    <mergeCell ref="L440:M440"/>
+    <mergeCell ref="R434:S434"/>
+    <mergeCell ref="R435:S435"/>
+    <mergeCell ref="L436:M436"/>
+    <mergeCell ref="R436:S436"/>
+    <mergeCell ref="L437:M437"/>
+    <mergeCell ref="R437:S437"/>
+    <mergeCell ref="R438:S438"/>
+    <mergeCell ref="L423:M423"/>
+    <mergeCell ref="L424:M424"/>
+    <mergeCell ref="L425:M425"/>
+    <mergeCell ref="R419:S419"/>
+    <mergeCell ref="R420:S420"/>
+    <mergeCell ref="L421:M421"/>
+    <mergeCell ref="R421:S421"/>
+    <mergeCell ref="L422:M422"/>
+    <mergeCell ref="R422:S422"/>
+    <mergeCell ref="R423:S423"/>
+    <mergeCell ref="L428:M428"/>
+    <mergeCell ref="L429:M429"/>
+    <mergeCell ref="L430:M430"/>
+    <mergeCell ref="R424:S424"/>
+    <mergeCell ref="R425:S425"/>
+    <mergeCell ref="L426:M426"/>
+    <mergeCell ref="R426:S426"/>
+    <mergeCell ref="L427:M427"/>
+    <mergeCell ref="R427:S427"/>
+    <mergeCell ref="R428:S428"/>
+    <mergeCell ref="L413:M413"/>
+    <mergeCell ref="L414:M414"/>
+    <mergeCell ref="L415:M415"/>
+    <mergeCell ref="R409:S409"/>
+    <mergeCell ref="R410:S410"/>
+    <mergeCell ref="L411:M411"/>
+    <mergeCell ref="R411:S411"/>
+    <mergeCell ref="L412:M412"/>
+    <mergeCell ref="R412:S412"/>
+    <mergeCell ref="R413:S413"/>
+    <mergeCell ref="L418:M418"/>
+    <mergeCell ref="L419:M419"/>
+    <mergeCell ref="L420:M420"/>
+    <mergeCell ref="R414:S414"/>
+    <mergeCell ref="R415:S415"/>
+    <mergeCell ref="L416:M416"/>
+    <mergeCell ref="R416:S416"/>
+    <mergeCell ref="L417:M417"/>
+    <mergeCell ref="R417:S417"/>
+    <mergeCell ref="R418:S418"/>
+    <mergeCell ref="L403:M403"/>
+    <mergeCell ref="L404:M404"/>
+    <mergeCell ref="L405:M405"/>
+    <mergeCell ref="R399:S399"/>
+    <mergeCell ref="R400:S400"/>
+    <mergeCell ref="L401:M401"/>
+    <mergeCell ref="R401:S401"/>
+    <mergeCell ref="L402:M402"/>
+    <mergeCell ref="R402:S402"/>
+    <mergeCell ref="R403:S403"/>
+    <mergeCell ref="L408:M408"/>
+    <mergeCell ref="L409:M409"/>
+    <mergeCell ref="L410:M410"/>
+    <mergeCell ref="R404:S404"/>
+    <mergeCell ref="R405:S405"/>
+    <mergeCell ref="L406:M406"/>
+    <mergeCell ref="R406:S406"/>
+    <mergeCell ref="L407:M407"/>
+    <mergeCell ref="R407:S407"/>
+    <mergeCell ref="R408:S408"/>
+    <mergeCell ref="L393:M393"/>
+    <mergeCell ref="L394:M394"/>
+    <mergeCell ref="L395:M395"/>
+    <mergeCell ref="R389:S389"/>
+    <mergeCell ref="R390:S390"/>
+    <mergeCell ref="L391:M391"/>
+    <mergeCell ref="R391:S391"/>
+    <mergeCell ref="L392:M392"/>
+    <mergeCell ref="R392:S392"/>
+    <mergeCell ref="R393:S393"/>
+    <mergeCell ref="L398:M398"/>
+    <mergeCell ref="L399:M399"/>
+    <mergeCell ref="L400:M400"/>
+    <mergeCell ref="R394:S394"/>
+    <mergeCell ref="R395:S395"/>
+    <mergeCell ref="L396:M396"/>
+    <mergeCell ref="R396:S396"/>
+    <mergeCell ref="L397:M397"/>
+    <mergeCell ref="R397:S397"/>
+    <mergeCell ref="R398:S398"/>
+    <mergeCell ref="L383:M383"/>
+    <mergeCell ref="L384:M384"/>
+    <mergeCell ref="L385:M385"/>
+    <mergeCell ref="R379:S379"/>
+    <mergeCell ref="R380:S380"/>
+    <mergeCell ref="L381:M381"/>
+    <mergeCell ref="R381:S381"/>
+    <mergeCell ref="L382:M382"/>
+    <mergeCell ref="R382:S382"/>
+    <mergeCell ref="R383:S383"/>
+    <mergeCell ref="L388:M388"/>
+    <mergeCell ref="L389:M389"/>
+    <mergeCell ref="L390:M390"/>
+    <mergeCell ref="R384:S384"/>
+    <mergeCell ref="R385:S385"/>
+    <mergeCell ref="L386:M386"/>
+    <mergeCell ref="R386:S386"/>
+    <mergeCell ref="L387:M387"/>
+    <mergeCell ref="R387:S387"/>
+    <mergeCell ref="R388:S388"/>
+    <mergeCell ref="L373:M373"/>
+    <mergeCell ref="L374:M374"/>
+    <mergeCell ref="L375:M375"/>
+    <mergeCell ref="R369:S369"/>
+    <mergeCell ref="R370:S370"/>
+    <mergeCell ref="L371:M371"/>
+    <mergeCell ref="R371:S371"/>
+    <mergeCell ref="L372:M372"/>
+    <mergeCell ref="R372:S372"/>
+    <mergeCell ref="R373:S373"/>
+    <mergeCell ref="L378:M378"/>
+    <mergeCell ref="L379:M379"/>
+    <mergeCell ref="L380:M380"/>
+    <mergeCell ref="R374:S374"/>
+    <mergeCell ref="R375:S375"/>
+    <mergeCell ref="L376:M376"/>
+    <mergeCell ref="R376:S376"/>
+    <mergeCell ref="L377:M377"/>
+    <mergeCell ref="R377:S377"/>
+    <mergeCell ref="R378:S378"/>
   </mergeCells>
   <pageMargins left="0.196850393700787" right="0.196850393700787" top="0.196850393700787" bottom="0.196850393700787" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
